--- a/ExportExcel/Edit Password Tests.xlsx
+++ b/ExportExcel/Edit Password Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="14">
   <si>
     <t>STT</t>
   </si>
@@ -41,43 +41,25 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20 ms</t>
-  </si>
-  <si>
-    <t>Success message should be displayed for: Hoa0987.team@gmail.com expected object to not be null</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>41 ms</t>
-  </si>
-  <si>
-    <t>34 ms</t>
-  </si>
-  <si>
-    <t>28 ms</t>
-  </si>
-  <si>
-    <t>47 ms</t>
-  </si>
-  <si>
-    <t>48 ms</t>
-  </si>
-  <si>
-    <t>24 ms</t>
-  </si>
-  <si>
-    <t>18 ms</t>
-  </si>
-  <si>
-    <t>46 ms</t>
-  </si>
-  <si>
-    <t>33 ms</t>
-  </si>
-  <si>
-    <t>61 ms</t>
+    <t>180009 ms</t>
+  </si>
+  <si>
+    <t>java.util.concurrent.TimeoutException
+Build info: version: '4.28.1', revision: '73f5ad48a2'
+System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
+Driver info: org.openqa.selenium.chrome.ChromeDriver
+Command: [6480e72fc2506c7674967deee16a95f4, get {url=https://totoday.vn/user/signin}]
+Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61570}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61570/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
+Session ID: 6480e72fc2506c7674967deee16a95f4</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
+  </si>
+  <si>
+    <t>0 ms</t>
+  </si>
+  <si>
+    <t>testChangePasswordWithSuccess</t>
   </si>
 </sst>
 </file>
@@ -148,11 +130,11 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="17.66796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="27.7109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="81.01171875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -205,7 +187,7 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="1">
+      <c r="D3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E3" t="s" s="0">
@@ -225,11 +207,11 @@
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="D4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>7</v>
@@ -245,11 +227,11 @@
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="1">
+      <c r="D5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>7</v>
@@ -265,11 +247,11 @@
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="1">
+      <c r="D6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>7</v>
@@ -285,11 +267,11 @@
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="1">
+      <c r="D7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -305,11 +287,11 @@
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="1">
+      <c r="D8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>7</v>
@@ -325,11 +307,11 @@
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="1">
+      <c r="D9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>7</v>
@@ -345,11 +327,11 @@
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="1">
+      <c r="D10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>7</v>
@@ -365,11 +347,11 @@
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="1">
+      <c r="D11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>7</v>
@@ -385,11 +367,11 @@
       <c r="C12" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D12" t="s" s="1">
+      <c r="D12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s" s="0">
         <v>7</v>
@@ -405,11 +387,11 @@
       <c r="C13" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D13" t="s" s="1">
+      <c r="D13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s" s="0">
         <v>7</v>
@@ -420,16 +402,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D14" t="s" s="1">
+      <c r="D14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s" s="0">
         <v>7</v>

--- a/ExportExcel/Edit Password Tests.xlsx
+++ b/ExportExcel/Edit Password Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
   <si>
     <t>STT</t>
   </si>
@@ -38,28 +38,49 @@
     <t/>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>180009 ms</t>
-  </si>
-  <si>
-    <t>java.util.concurrent.TimeoutException
-Build info: version: '4.28.1', revision: '73f5ad48a2'
-System info: os.name: 'Windows 11', os.arch: 'amd64', os.version: '10.0', java.version: '22.0.1'
-Driver info: org.openqa.selenium.chrome.ChromeDriver
-Command: [6480e72fc2506c7674967deee16a95f4, get {url=https://totoday.vn/user/signin}]
-Capabilities {acceptInsecureCerts: false, browserName: chrome, browserVersion: 134.0.6998.178, chrome: {chromedriverVersion: 134.0.6998.165 (fd886e2cb29..., userDataDir: C:\Users\A\AppData\Local\Te...}, fedcm:accounts: true, goog:chromeOptions: {debuggerAddress: localhost:61570}, networkConnectionEnabled: false, pageLoadStrategy: normal, platformName: windows, proxy: Proxy(), se:cdp: ws://localhost:61570/devtoo..., se:cdpVersion: 134.0.6998.178, setWindowRect: true, strictFileInteractability: false, timeouts: {implicit: 0, pageLoad: 300000, script: 30000}, unhandledPromptBehavior: dismiss and notify, webauthn:extension:credBlob: true, webauthn:extension:largeBlob: true, webauthn:extension:minPinLength: true, webauthn:extension:prf: true, webauthn:virtualAuthenticators: true}
-Session ID: 6480e72fc2506c7674967deee16a95f4</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
-  </si>
-  <si>
-    <t>0 ms</t>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>1921 ms</t>
+  </si>
+  <si>
+    <t>1300 ms</t>
+  </si>
+  <si>
+    <t>1270 ms</t>
+  </si>
+  <si>
+    <t>1661 ms</t>
+  </si>
+  <si>
+    <t>1416 ms</t>
+  </si>
+  <si>
+    <t>1700 ms</t>
+  </si>
+  <si>
+    <t>1887 ms</t>
+  </si>
+  <si>
+    <t>1522 ms</t>
+  </si>
+  <si>
+    <t>1730 ms</t>
+  </si>
+  <si>
+    <t>1512 ms</t>
+  </si>
+  <si>
+    <t>1256 ms</t>
+  </si>
+  <si>
+    <t>1376 ms</t>
   </si>
   <si>
     <t>testChangePasswordWithSuccess</t>
+  </si>
+  <si>
+    <t>8681 ms</t>
   </si>
 </sst>
 </file>
@@ -132,9 +153,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="27.7109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.57421875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -167,14 +188,14 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -187,11 +208,11 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>11</v>
+      <c r="D3" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>7</v>
@@ -207,11 +228,11 @@
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>11</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>12</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>7</v>
@@ -227,8 +248,8 @@
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>11</v>
+      <c r="D5" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>12</v>
@@ -247,11 +268,11 @@
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>11</v>
+      <c r="D6" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>7</v>
@@ -267,11 +288,11 @@
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="0">
-        <v>11</v>
+      <c r="D7" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -287,11 +308,11 @@
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="0">
-        <v>11</v>
+      <c r="D8" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>7</v>
@@ -307,11 +328,11 @@
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="0">
-        <v>11</v>
+      <c r="D9" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>7</v>
@@ -327,11 +348,11 @@
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="0">
-        <v>11</v>
+      <c r="D10" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>7</v>
@@ -347,11 +368,11 @@
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="0">
-        <v>11</v>
+      <c r="D11" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>7</v>
@@ -367,11 +388,11 @@
       <c r="C12" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D12" t="s" s="0">
-        <v>11</v>
+      <c r="D12" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="0">
         <v>7</v>
@@ -387,11 +408,11 @@
       <c r="C13" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D13" t="s" s="0">
-        <v>11</v>
+      <c r="D13" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s" s="0">
         <v>7</v>
@@ -402,16 +423,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D14" t="s" s="0">
-        <v>11</v>
+      <c r="D14" t="s" s="1">
+        <v>8</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s" s="0">
         <v>7</v>
